--- a/src/main/java/com/freecrm/testdata/create_contacts_testdata.xlsx
+++ b/src/main/java/com/freecrm/testdata/create_contacts_testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thndr\Desktop\Mission2026_QAAutomationProjects\FreeCrm\src\main\java\com\freecrm\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CDAE46-5550-4B50-880E-BEA60CA8C0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F791123F-01BE-4B77-95A5-04DF360FCE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -317,9 +317,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,131 +637,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>69</v>
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
